--- a/lib/cases/测试用例.xlsx
+++ b/lib/cases/测试用例.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="practice test automation" sheetId="1" r:id="rId1"/>
+    <sheet name="OrangeHRM" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="100">
   <si>
     <t>分组信息</t>
   </si>
@@ -280,7 +281,70 @@
     <t>TimeoutException</t>
   </si>
   <si>
-    <t>2</t>
+    <t>https://opensource-demo.orangehrmlive.com/web/index.php/auth/login</t>
+  </si>
+  <si>
+    <t>Input username</t>
+  </si>
+  <si>
+    <t>//input[@name='username']</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Input pwd</t>
+  </si>
+  <si>
+    <t>//input[@name='password']</t>
+  </si>
+  <si>
+    <t>admin123</t>
+  </si>
+  <si>
+    <t>Push  button</t>
+  </si>
+  <si>
+    <t>//button</t>
+  </si>
+  <si>
+    <t>//span[text()='Claim']</t>
+  </si>
+  <si>
+    <t>//a[text()='Employee Claims']</t>
+  </si>
+  <si>
+    <t>//button[text()=' Assign Claim ']</t>
+  </si>
+  <si>
+    <t>//input[@placeholder='Type for hints...']</t>
+  </si>
+  <si>
+    <t>Amelia  Brown</t>
+  </si>
+  <si>
+    <t>//label[text()='Event']/ancestor::div[contains(@class, 'oxd-input-group')]//div[@class='oxd-select-wrapper']</t>
+  </si>
+  <si>
+    <t>keyboard_navigate</t>
+  </si>
+  <si>
+    <t>down</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>//label[text()='Currency']/ancestor::div[contains(@class, 'oxd-input-group')]//div[@class='oxd-select-wrapper']</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>FALSE</t>
+  </si>
+  <si>
+    <t>quit</t>
   </si>
 </sst>
 </file>
@@ -938,6 +1002,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -946,15 +1019,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1283,881 +1347,883 @@
   <dimension ref="A1:I52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.2857142857143" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.4285714285714" style="2" customWidth="1"/>
-    <col min="3" max="3" width="41.8571428571429" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.0095238095238" style="2" customWidth="1"/>
-    <col min="5" max="5" width="63.6190476190476" style="2" customWidth="1"/>
-    <col min="6" max="6" width="24.1428571428571" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2" customWidth="1"/>
-    <col min="8" max="9" width="8.85714285714286" style="3"/>
+    <col min="1" max="1" width="11.2857142857143" style="5" customWidth="1"/>
+    <col min="2" max="2" width="25.4285714285714" style="5" customWidth="1"/>
+    <col min="3" max="3" width="41.8571428571429" style="5" customWidth="1"/>
+    <col min="4" max="4" width="19.0095238095238" style="5" customWidth="1"/>
+    <col min="5" max="5" width="63.6190476190476" style="5" customWidth="1"/>
+    <col min="6" max="6" width="24.1428571428571" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9" style="5" customWidth="1"/>
+    <col min="8" max="9" width="8.85714285714286" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:9">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="4" customFormat="1" ht="14.25" spans="1:9">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:9">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" customHeight="1" spans="1:9">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
     </row>
     <row r="4" customHeight="1" spans="1:9">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
     </row>
     <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
     </row>
     <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
     </row>
     <row r="7" customHeight="1" spans="1:9">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
     </row>
     <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
     </row>
     <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
     </row>
     <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
     </row>
     <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4" t="s">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
     </row>
     <row r="12" customHeight="1" spans="1:9">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4" t="s">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
     </row>
     <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
     </row>
     <row r="14" customHeight="1" spans="1:9">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
     </row>
     <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
     </row>
     <row r="16" customHeight="1" spans="1:9">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4" t="s">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
     </row>
     <row r="17" customHeight="1" spans="1:9">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4" t="s">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
     </row>
     <row r="18" customHeight="1" spans="1:9">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4" t="s">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
     </row>
     <row r="19" customHeight="1" spans="1:9">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4" t="s">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
     </row>
     <row r="20" customHeight="1" spans="1:9">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4" t="s">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
     </row>
     <row r="21" customHeight="1" spans="1:9">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4" t="s">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
     </row>
     <row r="22" customHeight="1" spans="1:9">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4" t="s">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
     </row>
     <row r="23" customHeight="1" spans="1:9">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4" t="s">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
     </row>
     <row r="24" customHeight="1" spans="1:9">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4" t="s">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
     </row>
     <row r="25" customHeight="1" spans="1:9">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4" t="s">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
     </row>
     <row r="26" customHeight="1" spans="1:9">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4" t="s">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
     </row>
     <row r="27" customHeight="1" spans="1:9">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4" t="s">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
     </row>
     <row r="28" customHeight="1" spans="1:9">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4" t="s">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
     </row>
     <row r="29" customHeight="1" spans="1:9">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
     </row>
     <row r="30" customHeight="1" spans="1:9">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4" t="s">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
     </row>
     <row r="31" customHeight="1" spans="1:9">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4" t="s">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
     </row>
     <row r="32" customHeight="1" spans="1:9">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4" t="s">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
     </row>
     <row r="33" customHeight="1" spans="1:9">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4" t="s">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
     </row>
     <row r="34" customHeight="1" spans="1:9">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4" t="s">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
     <row r="35" ht="14.25" spans="1:9">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4" t="s">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
     </row>
     <row r="36" customHeight="1" spans="1:9">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4" t="s">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
     </row>
     <row r="37" customHeight="1" spans="1:9">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4" t="s">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
     </row>
     <row r="38" ht="14.25" spans="1:9">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4" t="s">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="1:9">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4" t="s">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
     </row>
     <row r="40" customHeight="1" spans="1:9">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4" t="s">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
     </row>
     <row r="41" ht="14.25" spans="1:9">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4" t="s">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
     </row>
     <row r="42" customHeight="1" spans="1:9">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4" t="s">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="1:9">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4" t="s">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
     </row>
     <row r="44" ht="14.25" spans="1:9">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4" t="s">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
     </row>
     <row r="45" customHeight="1" spans="1:9">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4" t="s">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
     </row>
     <row r="46" customHeight="1" spans="1:9">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4" t="s">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="F46" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
     </row>
     <row r="47" customHeight="1" spans="1:9">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4" t="s">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
     </row>
     <row r="48" customHeight="1" spans="1:9">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4" t="s">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" customHeight="1" spans="2:9">
-      <c r="B49" s="4" t="s">
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+    </row>
+    <row r="49" customHeight="1" spans="1:9">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-    </row>
-    <row r="50" customHeight="1" spans="2:9">
-      <c r="B50" s="4"/>
-      <c r="C50" s="4" t="s">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+    </row>
+    <row r="50" customHeight="1" spans="1:9">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51" customHeight="1" spans="2:9">
-      <c r="B51" s="4"/>
-      <c r="C51" s="4" t="s">
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" customHeight="1" spans="1:9">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-    </row>
-    <row r="52" customHeight="1" spans="2:9">
-      <c r="B52" s="4"/>
-      <c r="C52" s="4" t="s">
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:9">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2182,4 +2248,316 @@
     <oddFooter>&amp;C&amp;F</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="11.5714285714286" customWidth="1"/>
+    <col min="2" max="2" width="19.4285714285714" customWidth="1"/>
+    <col min="3" max="4" width="15.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="77.2857142857143" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="8" max="9" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:9">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" ht="14.25" spans="1:9">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" ht="14.25" spans="1:9">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" ht="14.25" spans="1:9">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" ht="14.25" spans="1:9">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" ht="14.25" spans="1:9">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" ht="14.25" spans="1:9">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" ht="14.25" spans="1:9">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" ht="14.25" spans="1:9">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" ht="14.25" spans="1:9">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" ht="14.25" spans="1:9">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" ht="14.25" spans="1:9">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" ht="14.25" spans="1:9">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" ht="14.25" spans="1:9">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" ht="14.25" spans="1:9">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" ht="14.25" spans="1:9">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:G1"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H3">
+      <formula1>"FAIL,PASS"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" display="https://opensource-demo.orangehrmlive.com/web/index.php/auth/login" tooltip="https://opensource-demo.orangehrmlive.com/web/index.php/auth/login"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>